--- a/reference_keys/KEY_Video_2.xlsx
+++ b/reference_keys/KEY_Video_2.xlsx
@@ -5658,11 +5658,6 @@
           <t>Parts of Speech Present</t>
         </is>
       </c>
-      <c r="N265" t="inlineStr">
-        <is>
-          <t>Verb</t>
-        </is>
-      </c>
       <c r="P265" t="inlineStr">
         <is>
           <t>Preposition</t>

--- a/reference_keys/KEY_Video_2.xlsx
+++ b/reference_keys/KEY_Video_2.xlsx
@@ -560,7 +560,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>I MILK  PIZZA  BASKET FOOD CHICKEN BANANA GRAPE</t>
+          <t>I MILK PIZZA BASKET FOOD CHICKEN BANANA GRAPE</t>
         </is>
       </c>
     </row>
